--- a/factors/cicc_close_session_reverse/output/final_9_category_signals.xlsx
+++ b/factors/cicc_close_session_reverse/output/final_9_category_signals.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D87" t="b">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D88" t="b">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D89" t="b">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CROSSOVER</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="D98" t="b">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>daily=2681, minute=472295, events=1208</t>
+          <t>daily=2681, minute=472551, events=1208</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3615 threshold rows checked with source date &lt; signal date</t>
+          <t>3617 threshold rows checked with source date &lt; signal date</t>
         </is>
       </c>
     </row>

--- a/factors/cicc_close_session_reverse/output/final_9_category_signals.xlsx
+++ b/factors/cicc_close_session_reverse/output/final_9_category_signals.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="signals" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="factor_catalog" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="build_quality" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="threshold_audit" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -423,62 +436,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>signal_date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>trade_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>roll_status</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>block_signal</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>factor_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>display_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hold_days</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>signal</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43515</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43515</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -517,10 +530,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43539</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43539</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -559,10 +572,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43613</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43613</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -601,10 +614,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43626</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43626</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -643,10 +656,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43637</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43637</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -685,10 +698,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43685</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -727,10 +740,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43685</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -769,10 +782,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43685</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>43685</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -811,10 +824,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -853,10 +866,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -895,10 +908,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>43770</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -937,10 +950,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43773</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>43773</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -979,10 +992,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43845</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>43845</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -1021,10 +1034,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43873</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -1063,10 +1076,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43873</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1105,10 +1118,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43873</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>43873</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1147,10 +1160,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43888</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>43888</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -1189,10 +1202,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43893</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43893</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -1231,10 +1244,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43914</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43914</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -1273,10 +1286,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44039</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -1315,10 +1328,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>44039</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -1357,10 +1370,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>44039</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -1399,10 +1412,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44039</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>44039</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1441,10 +1454,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44070</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>44070</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1483,10 +1496,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44116</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>44116</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -1525,10 +1538,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44173</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>44173</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -1567,10 +1580,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>44173</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>44173</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1609,10 +1622,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>44173</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>44173</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -1651,10 +1664,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44174</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44174</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -1693,10 +1706,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44174</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44174</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -1735,10 +1748,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44223</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44223</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -1777,10 +1790,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44223</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44223</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -1819,10 +1832,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44223</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44223</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -1861,10 +1874,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44223</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44223</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -1903,10 +1916,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44278</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44278</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -1945,10 +1958,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44302</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -1987,10 +2000,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44330</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44330</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -2029,10 +2042,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44362</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44362</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -2071,10 +2084,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44389</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44389</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -2113,10 +2126,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44389</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44389</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2155,10 +2168,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44420</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44420</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -2197,10 +2210,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44536</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44536</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -2239,10 +2252,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44536</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44536</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -2281,10 +2294,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44536</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44536</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -2323,10 +2336,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44638</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44638</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -2365,10 +2378,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44711</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44711</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -2407,10 +2420,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2449,10 +2462,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44775</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44775</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -2491,10 +2504,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44851</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44851</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -2533,10 +2546,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44851</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44851</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -2575,10 +2588,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44911</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -2617,10 +2630,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44911</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -2659,10 +2672,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44971</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -2701,10 +2714,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44971</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -2743,10 +2756,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44971</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -2785,10 +2798,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45057</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45057</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -2827,10 +2840,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45182</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45182</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -2869,10 +2882,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45212</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -2911,10 +2924,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45212</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -2953,10 +2966,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45212</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -2995,10 +3008,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45212</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45212</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -3037,10 +3050,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45302</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45302</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -3079,10 +3092,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45356</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45356</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -3121,10 +3134,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45418</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -3163,10 +3176,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45418</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -3205,10 +3218,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45418</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45418</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -3247,10 +3260,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45419</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -3289,10 +3302,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45419</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -3331,10 +3344,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45419</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45419</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -3373,10 +3386,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45488</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45488</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -3415,10 +3428,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45495</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45495</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -3457,10 +3470,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45497</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>45497</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -3499,10 +3512,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>45527</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>45527</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -3541,10 +3554,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>45538</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>45538</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -3583,10 +3596,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>45576</v>
       </c>
-      <c r="B76" s="1" t="n">
+      <c r="B76" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -3625,10 +3638,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>45576</v>
       </c>
-      <c r="B77" s="1" t="n">
+      <c r="B77" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -3667,10 +3680,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>45576</v>
       </c>
-      <c r="B78" s="1" t="n">
+      <c r="B78" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -3709,10 +3722,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>45576</v>
       </c>
-      <c r="B79" s="1" t="n">
+      <c r="B79" s="2" t="n">
         <v>45576</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -3751,10 +3764,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>45579</v>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="2" t="n">
         <v>45579</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -3793,10 +3806,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45671</v>
       </c>
-      <c r="B81" s="1" t="n">
+      <c r="B81" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -3835,10 +3848,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45671</v>
       </c>
-      <c r="B82" s="1" t="n">
+      <c r="B82" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -3877,10 +3890,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45671</v>
       </c>
-      <c r="B83" s="1" t="n">
+      <c r="B83" s="2" t="n">
         <v>45671</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -3919,10 +3932,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45672</v>
       </c>
-      <c r="B84" s="1" t="n">
+      <c r="B84" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -3961,10 +3974,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45672</v>
       </c>
-      <c r="B85" s="1" t="n">
+      <c r="B85" s="2" t="n">
         <v>45672</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -4003,10 +4016,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45694</v>
       </c>
-      <c r="B86" s="1" t="n">
+      <c r="B86" s="2" t="n">
         <v>45694</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -4045,10 +4058,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45706</v>
       </c>
-      <c r="B87" s="1" t="n">
+      <c r="B87" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -4087,10 +4100,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45706</v>
       </c>
-      <c r="B88" s="1" t="n">
+      <c r="B88" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -4129,10 +4142,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45706</v>
       </c>
-      <c r="B89" s="1" t="n">
+      <c r="B89" s="2" t="n">
         <v>45706</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -4171,10 +4184,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45750</v>
       </c>
-      <c r="B90" s="1" t="n">
+      <c r="B90" s="2" t="n">
         <v>45750</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -4213,10 +4226,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45757</v>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -4255,10 +4268,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45757</v>
       </c>
-      <c r="B92" s="1" t="n">
+      <c r="B92" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -4297,10 +4310,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45757</v>
       </c>
-      <c r="B93" s="1" t="n">
+      <c r="B93" s="2" t="n">
         <v>45757</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -4339,10 +4352,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45783</v>
       </c>
-      <c r="B94" s="1" t="n">
+      <c r="B94" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -4381,10 +4394,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45790</v>
       </c>
-      <c r="B95" s="1" t="n">
+      <c r="B95" s="2" t="n">
         <v>45790</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -4423,10 +4436,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45790</v>
       </c>
-      <c r="B96" s="1" t="n">
+      <c r="B96" s="2" t="n">
         <v>45790</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -4465,10 +4478,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45790</v>
       </c>
-      <c r="B97" s="1" t="n">
+      <c r="B97" s="2" t="n">
         <v>45790</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -4507,10 +4520,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45792</v>
       </c>
-      <c r="B98" s="1" t="n">
+      <c r="B98" s="2" t="n">
         <v>45792</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -4549,10 +4562,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45796</v>
       </c>
-      <c r="B99" s="1" t="n">
+      <c r="B99" s="2" t="n">
         <v>45796</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -4591,10 +4604,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45796</v>
       </c>
-      <c r="B100" s="1" t="n">
+      <c r="B100" s="2" t="n">
         <v>45796</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -4633,10 +4646,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45796</v>
       </c>
-      <c r="B101" s="1" t="n">
+      <c r="B101" s="2" t="n">
         <v>45796</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -4675,10 +4688,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B102" s="1" t="n">
+      <c r="B102" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -4717,10 +4730,10 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -4759,10 +4772,10 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B104" s="1" t="n">
+      <c r="B104" s="2" t="n">
         <v>45855</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -4801,10 +4814,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B105" s="1" t="n">
+      <c r="B105" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -4843,10 +4856,10 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B106" s="1" t="n">
+      <c r="B106" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -4885,10 +4898,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="B107" s="1" t="n">
+      <c r="B107" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -4927,10 +4940,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45874</v>
       </c>
-      <c r="B108" s="1" t="n">
+      <c r="B108" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -4969,10 +4982,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45883</v>
       </c>
-      <c r="B109" s="1" t="n">
+      <c r="B109" s="2" t="n">
         <v>45883</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -5011,10 +5024,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45888</v>
       </c>
-      <c r="B110" s="1" t="n">
+      <c r="B110" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -5053,10 +5066,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45888</v>
       </c>
-      <c r="B111" s="1" t="n">
+      <c r="B111" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -5095,10 +5108,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45959</v>
       </c>
-      <c r="B112" s="1" t="n">
+      <c r="B112" s="2" t="n">
         <v>45959</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -5137,10 +5150,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B113" s="1" t="n">
+      <c r="B113" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -5179,10 +5192,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -5221,10 +5234,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B115" s="1" t="n">
+      <c r="B115" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -5263,10 +5276,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="B116" s="1" t="n">
+      <c r="B116" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="C116" t="inlineStr">
@@ -5305,10 +5318,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>45996</v>
       </c>
-      <c r="B117" s="1" t="n">
+      <c r="B117" s="2" t="n">
         <v>45996</v>
       </c>
       <c r="C117" t="inlineStr">
@@ -5347,10 +5360,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46126</v>
       </c>
-      <c r="B118" s="1" t="n">
+      <c r="B118" s="2" t="n">
         <v>46126</v>
       </c>
       <c r="C118" t="inlineStr">
@@ -5389,10 +5402,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="B119" s="1" t="n">
+      <c r="B119" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="C119" t="inlineStr">
@@ -5431,10 +5444,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="B120" s="1" t="n">
+      <c r="B120" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="C120" t="inlineStr">
@@ -5473,10 +5486,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46167</v>
       </c>
-      <c r="B121" s="1" t="n">
+      <c r="B121" s="2" t="n">
         <v>46167</v>
       </c>
       <c r="C121" t="inlineStr">
@@ -5515,10 +5528,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="B122" s="1" t="n">
+      <c r="B122" s="2" t="n">
         <v>46168</v>
       </c>
       <c r="C122" t="inlineStr">
@@ -5557,10 +5570,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="B123" s="1" t="n">
+      <c r="B123" s="2" t="n">
         <v>46168</v>
       </c>
       <c r="C123" t="inlineStr">
@@ -5599,10 +5612,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>46168</v>
       </c>
-      <c r="B124" s="1" t="n">
+      <c r="B124" s="2" t="n">
         <v>46168</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -5641,10 +5654,10 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>46178</v>
       </c>
-      <c r="B125" s="1" t="n">
+      <c r="B125" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -5683,10 +5696,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>46178</v>
       </c>
-      <c r="B126" s="1" t="n">
+      <c r="B126" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -5725,10 +5738,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>46178</v>
       </c>
-      <c r="B127" s="1" t="n">
+      <c r="B127" s="2" t="n">
         <v>46178</v>
       </c>
       <c r="C127" t="inlineStr">
@@ -5781,32 +5794,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>factor_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>display_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>hold_days</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>direction</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>formula</t>
         </is>
@@ -6097,17 +6110,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>check</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
@@ -6196,6 +6209,74 @@
         <is>
           <t>126 triggered signal rows</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>threshold_family</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>rows_checked</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>latest_signal_date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>latest_threshold_source_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>minute_segment_and_oi_rolls</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1793</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>daily_trend_vol_rolls</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1824</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>46213</v>
       </c>
     </row>
   </sheetData>
